--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8965,6 +8965,116 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122148567</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57734</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>688481</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6570517</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -8970,7 +8970,7 @@
         <v>122148567</v>
       </c>
       <c r="B68" t="n">
-        <v>57734</v>
+        <v>57738</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -8970,7 +8970,7 @@
         <v>122148567</v>
       </c>
       <c r="B68" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -8985,11 +8985,6 @@
       <c r="E68" t="n">
         <v>103015</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>Regulus regulus</t>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -8970,7 +8970,7 @@
         <v>122148567</v>
       </c>
       <c r="B68" t="n">
-        <v>57749</v>
+        <v>57753</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8984,6 +8984,11 @@
       </c>
       <c r="E68" t="n">
         <v>103015</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9075,6 +9075,120 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130238409</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91662</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>688203</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6570678</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Torrfura</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9189,6 +9189,108 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130238385</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91661</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>688214</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6570688</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Återfynd. Stående torrgran, på gren. Oktober 2021 var den frisk i toppen men nu helt torr</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6168,15 +6168,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>96005929</v>
+        <v>130251731</v>
       </c>
       <c r="B46" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92446</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6207,17 +6202,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tyresö slott, 500 m SSV slottet, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>688365.5894514072</v>
+        <v>688366</v>
       </c>
       <c r="R46" t="n">
-        <v>6570654.883410043</v>
+        <v>6570655</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6241,22 +6236,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Återfynd (2021). På knäckt gran(stubbe)</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6269,35 +6259,15 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Fingal Gyllang, Raul Vicente</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -9080,7 +9050,7 @@
         <v>130238409</v>
       </c>
       <c r="B69" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9194,7 +9164,7 @@
         <v>130238385</v>
       </c>
       <c r="B70" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9291,6 +9261,623 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>130252044</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91749</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>688418</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6570593</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130252054</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91749</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>688393</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6570567</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130251679</v>
+      </c>
+      <c r="B73" t="n">
+        <v>90774</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>889</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>688424</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6570561</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På torrfura</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>130252056</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91749</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>688385</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6570598</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>130251497</v>
+      </c>
+      <c r="B75" t="n">
+        <v>97166</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>688447</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6570544</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>130251920</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91749</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tyresö slott, barrskog SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>688419</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6570589</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9364,10 +9364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130251679</v>
+        <v>130252054</v>
       </c>
       <c r="B72" t="n">
-        <v>90774</v>
+        <v>91749</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688424</v>
+        <v>688393</v>
       </c>
       <c r="R72" t="n">
-        <v>6570561</v>
+        <v>6570567</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9438,11 +9438,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9470,10 +9465,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130252054</v>
+        <v>130251679</v>
       </c>
       <c r="B73" t="n">
-        <v>91749</v>
+        <v>90774</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9481,21 +9476,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9508,10 +9503,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688393</v>
+        <v>688424</v>
       </c>
       <c r="R73" t="n">
-        <v>6570567</v>
+        <v>6570561</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9544,6 +9539,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9364,10 +9364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130252054</v>
+        <v>130251679</v>
       </c>
       <c r="B72" t="n">
-        <v>91749</v>
+        <v>90774</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688393</v>
+        <v>688424</v>
       </c>
       <c r="R72" t="n">
-        <v>6570567</v>
+        <v>6570561</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9438,6 +9438,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9465,10 +9470,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130251679</v>
+        <v>130252054</v>
       </c>
       <c r="B73" t="n">
-        <v>90774</v>
+        <v>91749</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9476,21 +9481,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9503,10 +9508,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688424</v>
+        <v>688393</v>
       </c>
       <c r="R73" t="n">
-        <v>6570561</v>
+        <v>6570567</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9539,11 +9544,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130252056</v>
+        <v>130251497</v>
       </c>
       <c r="B74" t="n">
-        <v>91749</v>
+        <v>97166</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9582,26 +9582,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9609,10 +9610,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>688385</v>
+        <v>688447</v>
       </c>
       <c r="R74" t="n">
-        <v>6570598</v>
+        <v>6570544</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9645,6 +9646,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9672,10 +9678,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130251497</v>
+        <v>130252056</v>
       </c>
       <c r="B75" t="n">
-        <v>97166</v>
+        <v>91749</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9683,27 +9689,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9711,10 +9716,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>688447</v>
+        <v>688385</v>
       </c>
       <c r="R75" t="n">
-        <v>6570544</v>
+        <v>6570598</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9747,11 +9752,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10597,54 +10597,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351321</v>
+        <v>130351122</v>
       </c>
       <c r="B84" t="n">
-        <v>5177</v>
+        <v>91687</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>5445</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688906</v>
+        <v>688309</v>
       </c>
       <c r="R84" t="n">
-        <v>6570385</v>
+        <v>6570696</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10704,10 +10698,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351122</v>
+        <v>130351326</v>
       </c>
       <c r="B85" t="n">
-        <v>91687</v>
+        <v>91749</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,21 +10709,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10738,14 +10732,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688309</v>
+        <v>688902</v>
       </c>
       <c r="R85" t="n">
-        <v>6570696</v>
+        <v>6570364</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10805,37 +10799,43 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351326</v>
+        <v>130351321</v>
       </c>
       <c r="B86" t="n">
-        <v>91749</v>
+        <v>5177</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688902</v>
+        <v>688906</v>
       </c>
       <c r="R86" t="n">
-        <v>6570364</v>
+        <v>6570385</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9571,10 +9571,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130251497</v>
+        <v>130252056</v>
       </c>
       <c r="B74" t="n">
-        <v>97166</v>
+        <v>91749</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9582,27 +9582,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9610,10 +9609,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>688447</v>
+        <v>688385</v>
       </c>
       <c r="R74" t="n">
-        <v>6570544</v>
+        <v>6570598</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9646,11 +9645,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9678,10 +9672,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130252056</v>
+        <v>130251497</v>
       </c>
       <c r="B75" t="n">
-        <v>91749</v>
+        <v>97166</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,26 +9683,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9716,10 +9711,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>688385</v>
+        <v>688447</v>
       </c>
       <c r="R75" t="n">
-        <v>6570598</v>
+        <v>6570544</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9752,6 +9747,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10597,48 +10597,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351122</v>
+        <v>130351321</v>
       </c>
       <c r="B84" t="n">
-        <v>91687</v>
+        <v>5177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5445</v>
+        <v>100526</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688309</v>
+        <v>688906</v>
       </c>
       <c r="R84" t="n">
-        <v>6570696</v>
+        <v>6570385</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10698,10 +10704,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351326</v>
+        <v>130351122</v>
       </c>
       <c r="B85" t="n">
-        <v>91749</v>
+        <v>91687</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10709,21 +10715,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10732,14 +10738,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688902</v>
+        <v>688309</v>
       </c>
       <c r="R85" t="n">
-        <v>6570364</v>
+        <v>6570696</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10799,43 +10805,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351321</v>
+        <v>130351326</v>
       </c>
       <c r="B86" t="n">
-        <v>5177</v>
+        <v>91749</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688906</v>
+        <v>688902</v>
       </c>
       <c r="R86" t="n">
-        <v>6570385</v>
+        <v>6570364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -6171,7 +6171,7 @@
         <v>130251731</v>
       </c>
       <c r="B46" t="n">
-        <v>92446</v>
+        <v>92449</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>130238409</v>
       </c>
       <c r="B69" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>130238385</v>
       </c>
       <c r="B70" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>130252044</v>
       </c>
       <c r="B71" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>130251679</v>
       </c>
       <c r="B72" t="n">
-        <v>90774</v>
+        <v>90777</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>130252054</v>
       </c>
       <c r="B73" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9571,10 +9571,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130252056</v>
+        <v>130251497</v>
       </c>
       <c r="B74" t="n">
-        <v>91749</v>
+        <v>97169</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9582,26 +9582,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9609,10 +9610,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>688385</v>
+        <v>688447</v>
       </c>
       <c r="R74" t="n">
-        <v>6570598</v>
+        <v>6570544</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9645,6 +9646,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9672,10 +9678,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130251497</v>
+        <v>130252056</v>
       </c>
       <c r="B75" t="n">
-        <v>97166</v>
+        <v>91752</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9683,27 +9689,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9711,10 +9716,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>688447</v>
+        <v>688385</v>
       </c>
       <c r="R75" t="n">
-        <v>6570544</v>
+        <v>6570598</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9747,11 +9752,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9782,7 +9782,7 @@
         <v>130251920</v>
       </c>
       <c r="B76" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>130351126</v>
       </c>
       <c r="B77" t="n">
-        <v>91687</v>
+        <v>91690</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92446</v>
+        <v>92449</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>130351299</v>
       </c>
       <c r="B79" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>130351323</v>
       </c>
       <c r="B80" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>130351310</v>
       </c>
       <c r="B81" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>130351138</v>
       </c>
       <c r="B82" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92446</v>
+        <v>92449</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10597,54 +10597,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351321</v>
+        <v>130351122</v>
       </c>
       <c r="B84" t="n">
-        <v>5177</v>
+        <v>91690</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>5445</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688906</v>
+        <v>688309</v>
       </c>
       <c r="R84" t="n">
-        <v>6570385</v>
+        <v>6570696</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10704,10 +10698,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351122</v>
+        <v>130351326</v>
       </c>
       <c r="B85" t="n">
-        <v>91687</v>
+        <v>91752</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,21 +10709,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10738,14 +10732,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688309</v>
+        <v>688902</v>
       </c>
       <c r="R85" t="n">
-        <v>6570696</v>
+        <v>6570364</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10805,37 +10799,43 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351326</v>
+        <v>130351321</v>
       </c>
       <c r="B86" t="n">
-        <v>91749</v>
+        <v>5177</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688902</v>
+        <v>688906</v>
       </c>
       <c r="R86" t="n">
-        <v>6570364</v>
+        <v>6570385</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10909,7 +10909,7 @@
         <v>130351291</v>
       </c>
       <c r="B87" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>130351320</v>
       </c>
       <c r="B88" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -6171,7 +6171,7 @@
         <v>130251731</v>
       </c>
       <c r="B46" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>130238409</v>
       </c>
       <c r="B69" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>130238385</v>
       </c>
       <c r="B70" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>130252044</v>
       </c>
       <c r="B71" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>130251679</v>
       </c>
       <c r="B72" t="n">
-        <v>90777</v>
+        <v>90803</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>130252054</v>
       </c>
       <c r="B73" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>130251497</v>
       </c>
       <c r="B74" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>130252056</v>
       </c>
       <c r="B75" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>130251920</v>
       </c>
       <c r="B76" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>130351126</v>
       </c>
       <c r="B77" t="n">
-        <v>91690</v>
+        <v>91716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>130351299</v>
       </c>
       <c r="B79" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>130351323</v>
       </c>
       <c r="B80" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>130351310</v>
       </c>
       <c r="B81" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>130351138</v>
       </c>
       <c r="B82" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>130351122</v>
       </c>
       <c r="B84" t="n">
-        <v>91690</v>
+        <v>91716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>130351326</v>
       </c>
       <c r="B85" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>130351291</v>
       </c>
       <c r="B87" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>130351320</v>
       </c>
       <c r="B88" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -6171,7 +6171,7 @@
         <v>130251731</v>
       </c>
       <c r="B46" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>130238409</v>
       </c>
       <c r="B69" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>130238385</v>
       </c>
       <c r="B70" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>130252044</v>
       </c>
       <c r="B71" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9364,10 +9364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130251679</v>
+        <v>130252054</v>
       </c>
       <c r="B72" t="n">
-        <v>90803</v>
+        <v>91779</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688424</v>
+        <v>688393</v>
       </c>
       <c r="R72" t="n">
-        <v>6570561</v>
+        <v>6570567</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9438,11 +9438,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9470,10 +9465,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130252054</v>
+        <v>130251679</v>
       </c>
       <c r="B73" t="n">
-        <v>91778</v>
+        <v>90804</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9481,21 +9476,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9508,10 +9503,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688393</v>
+        <v>688424</v>
       </c>
       <c r="R73" t="n">
-        <v>6570567</v>
+        <v>6570561</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9544,6 +9539,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9574,7 +9574,7 @@
         <v>130251497</v>
       </c>
       <c r="B74" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>130252056</v>
       </c>
       <c r="B75" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>130251920</v>
       </c>
       <c r="B76" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>130351126</v>
       </c>
       <c r="B77" t="n">
-        <v>91716</v>
+        <v>91717</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>130351299</v>
       </c>
       <c r="B79" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>130351323</v>
       </c>
       <c r="B80" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>130351310</v>
       </c>
       <c r="B81" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>130351138</v>
       </c>
       <c r="B82" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10597,10 +10597,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351122</v>
+        <v>130351326</v>
       </c>
       <c r="B84" t="n">
-        <v>91716</v>
+        <v>91779</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10608,21 +10608,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10631,14 +10631,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688309</v>
+        <v>688902</v>
       </c>
       <c r="R84" t="n">
-        <v>6570696</v>
+        <v>6570364</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10698,10 +10698,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351326</v>
+        <v>130351122</v>
       </c>
       <c r="B85" t="n">
-        <v>91778</v>
+        <v>91717</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10709,21 +10709,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10732,14 +10732,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688902</v>
+        <v>688309</v>
       </c>
       <c r="R85" t="n">
-        <v>6570364</v>
+        <v>6570696</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10909,7 +10909,7 @@
         <v>130351291</v>
       </c>
       <c r="B87" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>130351320</v>
       </c>
       <c r="B88" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -6171,7 +6171,7 @@
         <v>130251731</v>
       </c>
       <c r="B46" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>130238409</v>
       </c>
       <c r="B69" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>130238385</v>
       </c>
       <c r="B70" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>130252044</v>
       </c>
       <c r="B71" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9364,10 +9364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130252054</v>
+        <v>130251679</v>
       </c>
       <c r="B72" t="n">
-        <v>91779</v>
+        <v>90805</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688393</v>
+        <v>688424</v>
       </c>
       <c r="R72" t="n">
-        <v>6570567</v>
+        <v>6570561</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9438,6 +9438,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9465,10 +9470,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130251679</v>
+        <v>130252054</v>
       </c>
       <c r="B73" t="n">
-        <v>90804</v>
+        <v>91780</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9476,21 +9481,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9503,10 +9508,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688424</v>
+        <v>688393</v>
       </c>
       <c r="R73" t="n">
-        <v>6570561</v>
+        <v>6570567</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9539,11 +9544,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9574,7 +9574,7 @@
         <v>130251497</v>
       </c>
       <c r="B74" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>130252056</v>
       </c>
       <c r="B75" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>130251920</v>
       </c>
       <c r="B76" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>130351126</v>
       </c>
       <c r="B77" t="n">
-        <v>91717</v>
+        <v>91718</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>130351299</v>
       </c>
       <c r="B79" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>130351323</v>
       </c>
       <c r="B80" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>130351310</v>
       </c>
       <c r="B81" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>130351138</v>
       </c>
       <c r="B82" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10597,37 +10597,43 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351326</v>
+        <v>130351321</v>
       </c>
       <c r="B84" t="n">
-        <v>91779</v>
+        <v>5177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10635,10 +10641,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688902</v>
+        <v>688906</v>
       </c>
       <c r="R84" t="n">
-        <v>6570364</v>
+        <v>6570385</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10701,7 +10707,7 @@
         <v>130351122</v>
       </c>
       <c r="B85" t="n">
-        <v>91717</v>
+        <v>91718</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10799,43 +10805,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351321</v>
+        <v>130351326</v>
       </c>
       <c r="B86" t="n">
-        <v>5177</v>
+        <v>91780</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688906</v>
+        <v>688902</v>
       </c>
       <c r="R86" t="n">
-        <v>6570385</v>
+        <v>6570364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10909,7 +10909,7 @@
         <v>130351291</v>
       </c>
       <c r="B87" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>130351320</v>
       </c>
       <c r="B88" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -6171,7 +6171,7 @@
         <v>130251731</v>
       </c>
       <c r="B46" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>130238409</v>
       </c>
       <c r="B69" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>130238385</v>
       </c>
       <c r="B70" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>130252044</v>
       </c>
       <c r="B71" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>130251679</v>
       </c>
       <c r="B72" t="n">
-        <v>90805</v>
+        <v>90807</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>130252054</v>
       </c>
       <c r="B73" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>130251497</v>
       </c>
       <c r="B74" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>130252056</v>
       </c>
       <c r="B75" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>130251920</v>
       </c>
       <c r="B76" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>130351126</v>
       </c>
       <c r="B77" t="n">
-        <v>91718</v>
+        <v>91720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>130351299</v>
       </c>
       <c r="B79" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>130351323</v>
       </c>
       <c r="B80" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>130351310</v>
       </c>
       <c r="B81" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>130351138</v>
       </c>
       <c r="B82" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10597,54 +10597,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351321</v>
+        <v>130351122</v>
       </c>
       <c r="B84" t="n">
-        <v>5177</v>
+        <v>91720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>5445</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688906</v>
+        <v>688309</v>
       </c>
       <c r="R84" t="n">
-        <v>6570385</v>
+        <v>6570696</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10704,10 +10698,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351122</v>
+        <v>130351326</v>
       </c>
       <c r="B85" t="n">
-        <v>91718</v>
+        <v>91782</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,21 +10709,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10738,14 +10732,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688309</v>
+        <v>688902</v>
       </c>
       <c r="R85" t="n">
-        <v>6570696</v>
+        <v>6570364</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10805,37 +10799,43 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351326</v>
+        <v>130351321</v>
       </c>
       <c r="B86" t="n">
-        <v>91780</v>
+        <v>5177</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688902</v>
+        <v>688906</v>
       </c>
       <c r="R86" t="n">
-        <v>6570364</v>
+        <v>6570385</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10909,7 +10909,7 @@
         <v>130351291</v>
       </c>
       <c r="B87" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>130351320</v>
       </c>
       <c r="B88" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -6171,7 +6171,7 @@
         <v>130251731</v>
       </c>
       <c r="B46" t="n">
-        <v>92479</v>
+        <v>92483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>130251497</v>
       </c>
       <c r="B74" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92479</v>
+        <v>92483</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92479</v>
+        <v>92483</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9364,10 +9364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130251679</v>
+        <v>130252054</v>
       </c>
       <c r="B72" t="n">
-        <v>90807</v>
+        <v>91782</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688424</v>
+        <v>688393</v>
       </c>
       <c r="R72" t="n">
-        <v>6570561</v>
+        <v>6570567</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9438,11 +9438,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9470,10 +9465,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130252054</v>
+        <v>130251679</v>
       </c>
       <c r="B73" t="n">
-        <v>91782</v>
+        <v>90807</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9481,21 +9476,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9508,10 +9503,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688393</v>
+        <v>688424</v>
       </c>
       <c r="R73" t="n">
-        <v>6570567</v>
+        <v>6570561</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9544,6 +9539,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130251497</v>
+        <v>130252056</v>
       </c>
       <c r="B74" t="n">
-        <v>97203</v>
+        <v>91782</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9582,27 +9582,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9610,10 +9609,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>688447</v>
+        <v>688385</v>
       </c>
       <c r="R74" t="n">
-        <v>6570544</v>
+        <v>6570598</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9646,11 +9645,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9678,10 +9672,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130252056</v>
+        <v>130251497</v>
       </c>
       <c r="B75" t="n">
-        <v>91782</v>
+        <v>97203</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,26 +9683,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9716,10 +9711,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>688385</v>
+        <v>688447</v>
       </c>
       <c r="R75" t="n">
-        <v>6570598</v>
+        <v>6570544</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9752,6 +9747,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10597,48 +10597,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351122</v>
+        <v>130351321</v>
       </c>
       <c r="B84" t="n">
-        <v>91720</v>
+        <v>5177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5445</v>
+        <v>100526</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688309</v>
+        <v>688906</v>
       </c>
       <c r="R84" t="n">
-        <v>6570696</v>
+        <v>6570385</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10698,10 +10704,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351326</v>
+        <v>130351122</v>
       </c>
       <c r="B85" t="n">
-        <v>91782</v>
+        <v>91720</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10709,21 +10715,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10732,14 +10738,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688902</v>
+        <v>688309</v>
       </c>
       <c r="R85" t="n">
-        <v>6570364</v>
+        <v>6570696</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10799,43 +10805,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351321</v>
+        <v>130351326</v>
       </c>
       <c r="B86" t="n">
-        <v>5177</v>
+        <v>91782</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688906</v>
+        <v>688902</v>
       </c>
       <c r="R86" t="n">
-        <v>6570385</v>
+        <v>6570364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9364,10 +9364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130252054</v>
+        <v>130251679</v>
       </c>
       <c r="B72" t="n">
-        <v>91782</v>
+        <v>90807</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688393</v>
+        <v>688424</v>
       </c>
       <c r="R72" t="n">
-        <v>6570567</v>
+        <v>6570561</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9438,6 +9438,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9465,10 +9470,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130251679</v>
+        <v>130252054</v>
       </c>
       <c r="B73" t="n">
-        <v>90807</v>
+        <v>91782</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9476,21 +9481,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9503,10 +9508,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688424</v>
+        <v>688393</v>
       </c>
       <c r="R73" t="n">
-        <v>6570561</v>
+        <v>6570567</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9539,11 +9544,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130252056</v>
+        <v>130251497</v>
       </c>
       <c r="B74" t="n">
-        <v>91782</v>
+        <v>97203</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9582,26 +9582,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9609,10 +9610,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>688385</v>
+        <v>688447</v>
       </c>
       <c r="R74" t="n">
-        <v>6570598</v>
+        <v>6570544</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9645,6 +9646,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9672,10 +9678,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130251497</v>
+        <v>130252056</v>
       </c>
       <c r="B75" t="n">
-        <v>97203</v>
+        <v>91782</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9683,27 +9689,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9711,10 +9716,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>688447</v>
+        <v>688385</v>
       </c>
       <c r="R75" t="n">
-        <v>6570544</v>
+        <v>6570598</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9747,11 +9752,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10597,54 +10597,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351321</v>
+        <v>130351122</v>
       </c>
       <c r="B84" t="n">
-        <v>5177</v>
+        <v>91720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>5445</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688906</v>
+        <v>688309</v>
       </c>
       <c r="R84" t="n">
-        <v>6570385</v>
+        <v>6570696</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10704,10 +10698,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351122</v>
+        <v>130351326</v>
       </c>
       <c r="B85" t="n">
-        <v>91720</v>
+        <v>91782</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,21 +10709,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10738,14 +10732,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688309</v>
+        <v>688902</v>
       </c>
       <c r="R85" t="n">
-        <v>6570696</v>
+        <v>6570364</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10805,37 +10799,43 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351326</v>
+        <v>130351321</v>
       </c>
       <c r="B86" t="n">
-        <v>91782</v>
+        <v>5177</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688902</v>
+        <v>688906</v>
       </c>
       <c r="R86" t="n">
-        <v>6570364</v>
+        <v>6570385</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9364,10 +9364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130251679</v>
+        <v>130252054</v>
       </c>
       <c r="B72" t="n">
-        <v>90807</v>
+        <v>91782</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9375,21 +9375,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688424</v>
+        <v>688393</v>
       </c>
       <c r="R72" t="n">
-        <v>6570561</v>
+        <v>6570567</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9438,11 +9438,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9470,10 +9465,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130252054</v>
+        <v>130251679</v>
       </c>
       <c r="B73" t="n">
-        <v>91782</v>
+        <v>90807</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9481,21 +9476,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9508,10 +9503,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688393</v>
+        <v>688424</v>
       </c>
       <c r="R73" t="n">
-        <v>6570567</v>
+        <v>6570561</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9544,6 +9539,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På torrfura</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130251497</v>
+        <v>130252056</v>
       </c>
       <c r="B74" t="n">
-        <v>97203</v>
+        <v>91782</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9582,27 +9582,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9610,10 +9609,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>688447</v>
+        <v>688385</v>
       </c>
       <c r="R74" t="n">
-        <v>6570544</v>
+        <v>6570598</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9646,11 +9645,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9678,10 +9672,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130252056</v>
+        <v>130251497</v>
       </c>
       <c r="B75" t="n">
-        <v>91782</v>
+        <v>97203</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,26 +9683,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9716,10 +9711,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>688385</v>
+        <v>688447</v>
       </c>
       <c r="R75" t="n">
-        <v>6570598</v>
+        <v>6570544</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9752,6 +9747,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Återfynd  (2018) på granlåga (samma som gränsticka men 5-6 m mer åt syd)). 10x2 cm</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9883,7 +9883,7 @@
         <v>130351126</v>
       </c>
       <c r="B77" t="n">
-        <v>91720</v>
+        <v>91732</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92483</v>
+        <v>92496</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>130351299</v>
       </c>
       <c r="B79" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>130351323</v>
       </c>
       <c r="B80" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>130351310</v>
       </c>
       <c r="B81" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>130351138</v>
       </c>
       <c r="B82" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92483</v>
+        <v>92496</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10597,48 +10597,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351122</v>
+        <v>130351321</v>
       </c>
       <c r="B84" t="n">
-        <v>91720</v>
+        <v>5177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5445</v>
+        <v>100526</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688309</v>
+        <v>688906</v>
       </c>
       <c r="R84" t="n">
-        <v>6570696</v>
+        <v>6570385</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10698,10 +10704,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351326</v>
+        <v>130351122</v>
       </c>
       <c r="B85" t="n">
-        <v>91782</v>
+        <v>91732</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10709,21 +10715,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10732,14 +10738,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688902</v>
+        <v>688309</v>
       </c>
       <c r="R85" t="n">
-        <v>6570364</v>
+        <v>6570696</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10799,43 +10805,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351321</v>
+        <v>130351326</v>
       </c>
       <c r="B86" t="n">
-        <v>5177</v>
+        <v>91795</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688906</v>
+        <v>688902</v>
       </c>
       <c r="R86" t="n">
-        <v>6570385</v>
+        <v>6570364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10909,7 +10909,7 @@
         <v>130351291</v>
       </c>
       <c r="B87" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>130351320</v>
       </c>
       <c r="B88" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9883,7 +9883,7 @@
         <v>130351126</v>
       </c>
       <c r="B77" t="n">
-        <v>91732</v>
+        <v>91733</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>130351299</v>
       </c>
       <c r="B79" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>130351323</v>
       </c>
       <c r="B80" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>130351310</v>
       </c>
       <c r="B81" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>130351138</v>
       </c>
       <c r="B82" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10597,54 +10597,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351321</v>
+        <v>130351122</v>
       </c>
       <c r="B84" t="n">
-        <v>5177</v>
+        <v>91733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>5445</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688906</v>
+        <v>688309</v>
       </c>
       <c r="R84" t="n">
-        <v>6570385</v>
+        <v>6570696</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10704,48 +10698,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351122</v>
+        <v>130351321</v>
       </c>
       <c r="B85" t="n">
-        <v>91732</v>
+        <v>5177</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5445</v>
+        <v>100526</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688309</v>
+        <v>688906</v>
       </c>
       <c r="R85" t="n">
-        <v>6570696</v>
+        <v>6570385</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10808,7 +10808,7 @@
         <v>130351326</v>
       </c>
       <c r="B86" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>130351291</v>
       </c>
       <c r="B87" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>130351320</v>
       </c>
       <c r="B88" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -9883,7 +9883,7 @@
         <v>130351126</v>
       </c>
       <c r="B77" t="n">
-        <v>91733</v>
+        <v>91734</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>130351337</v>
       </c>
       <c r="B78" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>130351299</v>
       </c>
       <c r="B79" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>130351323</v>
       </c>
       <c r="B80" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>130351310</v>
       </c>
       <c r="B81" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>130351138</v>
       </c>
       <c r="B82" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>130351132</v>
       </c>
       <c r="B83" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10597,48 +10597,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351122</v>
+        <v>130351321</v>
       </c>
       <c r="B84" t="n">
-        <v>91733</v>
+        <v>5177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5445</v>
+        <v>100526</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688309</v>
+        <v>688906</v>
       </c>
       <c r="R84" t="n">
-        <v>6570696</v>
+        <v>6570385</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10698,54 +10704,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351321</v>
+        <v>130351122</v>
       </c>
       <c r="B85" t="n">
-        <v>5177</v>
+        <v>91734</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100526</v>
+        <v>5445</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688906</v>
+        <v>688309</v>
       </c>
       <c r="R85" t="n">
-        <v>6570385</v>
+        <v>6570696</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10808,7 +10808,7 @@
         <v>130351326</v>
       </c>
       <c r="B86" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>130351291</v>
       </c>
       <c r="B87" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>130351320</v>
       </c>
       <c r="B88" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -10597,54 +10597,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351321</v>
+        <v>130351122</v>
       </c>
       <c r="B84" t="n">
-        <v>5177</v>
+        <v>91734</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>5445</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688906</v>
+        <v>688309</v>
       </c>
       <c r="R84" t="n">
-        <v>6570385</v>
+        <v>6570696</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10704,10 +10698,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351122</v>
+        <v>130351326</v>
       </c>
       <c r="B85" t="n">
-        <v>91734</v>
+        <v>91797</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10715,21 +10709,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10738,14 +10732,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688309</v>
+        <v>688902</v>
       </c>
       <c r="R85" t="n">
-        <v>6570696</v>
+        <v>6570364</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10805,37 +10799,43 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351326</v>
+        <v>130351321</v>
       </c>
       <c r="B86" t="n">
-        <v>91797</v>
+        <v>5177</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688902</v>
+        <v>688906</v>
       </c>
       <c r="R86" t="n">
-        <v>6570364</v>
+        <v>6570385</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -10597,48 +10597,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130351122</v>
+        <v>130351321</v>
       </c>
       <c r="B84" t="n">
-        <v>91734</v>
+        <v>5177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5445</v>
+        <v>100526</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Prinsvillan S om, Srm</t>
+          <t>Tyresö slott, barrskog S om, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688309</v>
+        <v>688906</v>
       </c>
       <c r="R84" t="n">
-        <v>6570696</v>
+        <v>6570385</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10698,10 +10704,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130351326</v>
+        <v>130351122</v>
       </c>
       <c r="B85" t="n">
-        <v>91797</v>
+        <v>91734</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10709,21 +10715,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10732,14 +10738,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tyresö slott, barrskog S om, Srm</t>
+          <t>Prinsvillan S om, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688902</v>
+        <v>688309</v>
       </c>
       <c r="R85" t="n">
-        <v>6570364</v>
+        <v>6570696</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10799,43 +10805,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130351321</v>
+        <v>130351326</v>
       </c>
       <c r="B86" t="n">
-        <v>5177</v>
+        <v>91797</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688906</v>
+        <v>688902</v>
       </c>
       <c r="R86" t="n">
-        <v>6570385</v>
+        <v>6570364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11111,6 +11111,344 @@
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>131206476</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SV slottsparken, Tyresö slott, Srm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>688573</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6570596</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ronny Högström</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ronny Högström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>131206475</v>
+      </c>
+      <c r="B90" t="n">
+        <v>91829</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Brant S Tyresö slott, Tyresö slott, Srm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>688545</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6570548</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ronny Högström</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ronny Högström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>131206465</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91819</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Brant S Tyresö slott, Tyresö slott, Srm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>688545</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6570548</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På bäverfälld grov asp.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ronny Högström</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ronny Högström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91819</v>
+        <v>91820</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91830</v>
+        <v>91831</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91830</v>
+        <v>91831</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91820</v>
+        <v>91821</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91831</v>
+        <v>91834</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91831</v>
+        <v>91834</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91821</v>
+        <v>91824</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11449,6 +11449,144 @@
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>131365954</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91835</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Tyresö 1:7, Srm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>688504</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6570552</v>
+      </c>
+      <c r="S92" t="n">
+        <v>33</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Tyresö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Nils MAGNUS Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Nils MAGNUS Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>131365954</v>
       </c>
       <c r="B92" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91827</v>
+        <v>91828</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>131365954</v>
       </c>
       <c r="B92" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>131365954</v>
       </c>
       <c r="B92" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>131365954</v>
       </c>
       <c r="B92" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -11116,7 +11116,7 @@
         <v>131206476</v>
       </c>
       <c r="B89" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>131206475</v>
       </c>
       <c r="B90" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>131206465</v>
       </c>
       <c r="B91" t="n">
-        <v>91832</v>
+        <v>91833</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>131365954</v>
       </c>
       <c r="B92" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 60923-2021 artfynd.xlsx
+++ b/artfynd/A 60923-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71076603</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077284</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251497</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077461</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79871712</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79976618</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005997</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1719,6 +1764,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96006195</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1838,6 +1888,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96007629</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1944,6 +1999,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90295172</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90295191</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2156,6 +2221,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90295206</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2267,6 +2337,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91139925</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2373,6 +2448,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251679</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2479,6 +2559,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351291</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2585,6 +2670,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351310</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2686,6 +2776,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351320</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2815,6 +2910,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96006075</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2929,6 +3029,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96879718</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3042,6 +3147,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077074</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3156,6 +3266,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90295254</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3278,6 +3393,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98184853</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3394,6 +3514,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131206465</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3521,6 +3646,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80932831</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3626,6 +3756,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077395</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3731,6 +3866,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71079473</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3836,6 +3976,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71076631</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3941,6 +4086,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077017</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4046,6 +4196,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078053</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4151,6 +4306,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078203</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4256,6 +4416,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078661</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4361,6 +4526,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078692</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4466,6 +4636,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71079007</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4573,6 +4748,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96007588</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4675,6 +4855,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96879733</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4777,6 +4962,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97177388</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4899,6 +5089,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97177386</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5009,6 +5204,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111683845</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5130,6 +5330,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96005929</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5236,6 +5441,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251731</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5337,6 +5547,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351132</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5443,6 +5658,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351314</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5544,6 +5764,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351337</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5652,6 +5877,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98184193</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5752,6 +5982,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67748563</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5852,6 +6087,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67748568</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5958,6 +6198,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96007657</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6072,6 +6317,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96006025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6190,6 +6440,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111683850</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6290,6 +6545,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67748588</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6390,6 +6650,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67748619</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6495,6 +6760,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71076709</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6600,6 +6870,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71076758</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6705,6 +6980,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71076778</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6818,6 +7098,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077091</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6931,6 +7216,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077152</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7044,6 +7334,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077338</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7149,6 +7444,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077492</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7254,6 +7554,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077518</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7359,6 +7664,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077569</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7464,6 +7774,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077677</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7569,6 +7884,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71077722</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7682,6 +8002,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93076630</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7788,6 +8113,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96879806</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7906,6 +8236,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116060181</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8020,6 +8355,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130238409</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8121,6 +8461,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251859</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8222,6 +8567,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251920</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8323,6 +8673,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251973</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8424,6 +8779,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252037</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8525,6 +8885,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252044</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8626,6 +8991,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252054</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8727,6 +9097,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252056</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8833,6 +9208,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351138</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8934,6 +9314,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351299</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9035,6 +9420,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351323</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9136,6 +9526,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351326</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9237,6 +9632,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351327</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9348,6 +9748,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131206474</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9459,6 +9864,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131206476</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9597,6 +10007,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131365954</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9710,6 +10125,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078729</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9823,6 +10243,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078751</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9924,6 +10349,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351122</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10025,6 +10455,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351126</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10130,6 +10565,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71076613</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10259,6 +10699,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96006045</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10373,6 +10818,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96007584</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10487,6 +10937,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111683852</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10597,6 +11052,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111683853</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10697,6 +11157,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67748583</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10818,6 +11283,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107530689</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10922,6 +11392,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078850</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11026,6 +11501,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71079112</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11130,6 +11610,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71079276</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11234,6 +11719,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078908</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11348,6 +11838,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97177408</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11457,6 +11952,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132068906</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11564,6 +12064,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351321</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11716,6 +12221,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80976096</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11827,6 +12337,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71076656</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11936,6 +12451,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97177409</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12042,6 +12562,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70932584</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12153,6 +12678,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078795</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12277,6 +12807,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133569078</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12391,6 +12926,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99158608</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12496,6 +13036,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122148567</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12615,6 +13160,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82104747</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12726,6 +13276,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111683856</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12831,6 +13386,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078898</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12936,6 +13496,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71079159</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13041,6 +13606,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71079447</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13146,6 +13716,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71078836</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13251,8 +13826,130 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71079100</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>